--- a/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
@@ -2227,7 +2227,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ㅋ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -2337,7 +2337,7 @@
       <c r="M5" s="22"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄴ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O5" s="22"/>
@@ -2372,11 +2372,7 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
     </row>
     <row r="7" ht="90.33" customHeight="true">
@@ -2391,24 +2387,17 @@
         </is>
       </c>
       <c r="G7" s="22"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹‹</t>
-        </is>
-      </c>
+      <c r="H7" s="21"/>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -2567,18 +2556,9 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21"/>
       <c r="G12" s="22"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H12" s="21"/>
       <c r="I12" s="22"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="J12" s="21"/>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -2586,12 +2566,7 @@
         </is>
       </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="N12" s="21"/>
       <c r="O12" s="22"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
@@ -2227,7 +2227,7 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋ㅋ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
@@ -2337,7 +2337,7 @@
       <c r="M5" s="22"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄴ</t>
         </is>
       </c>
       <c r="O5" s="22"/>
@@ -2372,7 +2372,11 @@
         </is>
       </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O6" s="22"/>
     </row>
     <row r="7" ht="90.33" customHeight="true">
@@ -2387,7 +2391,11 @@
         </is>
       </c>
       <c r="G7" s="22"/>
-      <c r="H7" s="21"/>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="I7" s="22"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
@@ -2558,7 +2566,11 @@
       <c r="G12" s="22"/>
       <c r="H12" s="21"/>
       <c r="I12" s="22"/>
-      <c r="J12" s="21"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
@@ -2566,7 +2578,11 @@
         </is>
       </c>
       <c r="M12" s="22"/>
-      <c r="N12" s="21"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="O12" s="22"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
+++ b/sheets/조재수대금교본/검수/대금 시나위 (4).xlsx
@@ -2183,26 +2183,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="50.63" customHeight="true">
+    <row r="2" ht="56.34" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="90.33" customHeight="true">
+    <row r="3" ht="100.57" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="90.33" customHeight="true">
+    <row r="4" ht="100.57" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="22"/>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="O4" s="22"/>
     </row>
-    <row r="5" ht="90.33" customHeight="true">
+    <row r="5" ht="100.57" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="O5" s="22"/>
     </row>
-    <row r="6" ht="90.33" customHeight="true">
+    <row r="6" ht="100.57" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="90.33" customHeight="true">
+    <row r="7" ht="100.57" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2412,7 +2412,7 @@
       <c r="N7" s="21"/>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="90.33" customHeight="true">
+    <row r="8" ht="100.57" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       <c r="N8" s="21"/>
       <c r="O8" s="22"/>
     </row>
-    <row r="9" ht="90.33" customHeight="true">
+    <row r="9" ht="100.57" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2482,7 +2482,7 @@
       <c r="N9" s="21"/>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="90.33" customHeight="true">
+    <row r="10" ht="100.57" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -2515,7 +2515,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="22"/>
     </row>
-    <row r="11" ht="90.33" customHeight="true">
+    <row r="11" ht="100.57" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2548,7 +2548,7 @@
       <c r="N11" s="21"/>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="90.33" customHeight="true">
+    <row r="12" ht="100.57" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2591,6 +2591,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="79"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="71"/>
 </worksheet>
 </file>